--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoKetQuaHocTapIELTS.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoKetQuaHocTapIELTS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FF878D-3385-424E-89BF-9272A4ECD264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60682F78-EF53-4FD2-AC44-AEAC34BDCCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0D544DFD-F0B4-4797-9334-D0119CA48DC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0D544DFD-F0B4-4797-9334-D0119CA48DC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
   <si>
     <t>BÁO CÁO KẾT QUẢ HỌC TẬP (IELTS)</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>Unit 5 : {0}</t>
+  </si>
+  <si>
+    <t>UserName</t>
   </si>
 </sst>
 </file>
@@ -452,12 +455,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -475,6 +472,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -792,98 +795,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB323575-7255-4E3A-A299-F4AE49204E82}">
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.375" customWidth="1"/>
-    <col min="2" max="3" width="21.75" customWidth="1"/>
-    <col min="4" max="4" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="28.625" customWidth="1"/>
-    <col min="6" max="6" width="21.625" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
-    <col min="8" max="8" width="31.125" style="9" customWidth="1"/>
-    <col min="9" max="9" width="27.875" customWidth="1"/>
-    <col min="10" max="10" width="28.625" customWidth="1"/>
-    <col min="11" max="11" width="27.25" customWidth="1"/>
-    <col min="12" max="12" width="20.875" customWidth="1"/>
+    <col min="1" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="4" width="21.75" customWidth="1"/>
+    <col min="5" max="5" width="15.875" customWidth="1"/>
+    <col min="6" max="6" width="28.625" customWidth="1"/>
+    <col min="7" max="7" width="21.625" customWidth="1"/>
+    <col min="8" max="8" width="22.375" customWidth="1"/>
+    <col min="9" max="9" width="31.125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="27.875" customWidth="1"/>
+    <col min="11" max="11" width="28.625" customWidth="1"/>
+    <col min="12" max="12" width="27.25" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:37" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="21"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="21"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="21"/>
-      <c r="AH1" s="21"/>
-      <c r="AI1" s="21"/>
-      <c r="AJ1" s="21"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
     </row>
-    <row r="2" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="8" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="2"/>
+      <c r="M2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="8"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="1"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
@@ -903,28 +907,29 @@
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="8">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="8">
         <v>120</v>
       </c>
-      <c r="F3" s="8"/>
       <c r="G3" s="8"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="10"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
-      <c r="L3" s="11"/>
+      <c r="L3" s="8"/>
       <c r="M3" s="11"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="2"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="3"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
@@ -945,32 +950,33 @@
       <c r="AH3" s="2"/>
       <c r="AI3" s="2"/>
       <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="12" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="8"/>
+      <c r="I4" s="10"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="11"/>
+      <c r="L4" s="8"/>
       <c r="M4" s="11"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="2"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="3"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
@@ -991,32 +997,33 @@
       <c r="AH4" s="2"/>
       <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="12" t="s">
-        <v>49</v>
-      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="12" t="s">
         <v>49</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="8"/>
+      <c r="H5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="10"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="11"/>
+      <c r="L5" s="8"/>
       <c r="M5" s="11"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="2"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="3"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
@@ -1037,32 +1044,33 @@
       <c r="AH5" s="2"/>
       <c r="AI5" s="2"/>
       <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
     </row>
-    <row r="6" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="12" t="s">
-        <v>49</v>
-      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="8"/>
+      <c r="H6" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="10"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="11"/>
+      <c r="L6" s="8"/>
       <c r="M6" s="11"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="2"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="3"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -1083,28 +1091,29 @@
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
     </row>
-    <row r="7" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="8" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="10"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="11"/>
+      <c r="L7" s="8"/>
       <c r="M7" s="11"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="2"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="3"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
@@ -1125,79 +1134,79 @@
       <c r="AH7" s="2"/>
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2"/>
+      <c r="AK7" s="2"/>
     </row>
-    <row r="8" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="10" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="I8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="L8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="M8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="15"/>
-      <c r="AB8" s="15"/>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="15"/>
-      <c r="AI8" s="15"/>
-      <c r="AJ8" s="15"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+      <c r="AG8" s="23"/>
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="23"/>
+      <c r="AJ8" s="23"/>
+      <c r="AK8" s="23"/>
     </row>
-    <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="10" t="s">
+    <row r="9" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>48</v>
@@ -1211,175 +1220,181 @@
       <c r="L9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="24"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="16"/>
-      <c r="AJ9" s="16"/>
+      <c r="M9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="22"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="24"/>
     </row>
-    <row r="10" spans="1:36" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="M10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="N10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="O10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="P10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="Q10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" s="5" t="s">
+      <c r="R10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="R10" s="5" t="s">
+      <c r="S10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S10" s="5" t="s">
+      <c r="T10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="T10" s="5" t="s">
+      <c r="U10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="7" t="s">
+      <c r="V10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="V10" s="5" t="s">
+      <c r="W10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="W10" s="5" t="s">
+      <c r="X10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="X10" s="5" t="s">
+      <c r="Y10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Z10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="Z10" s="5" t="s">
+      <c r="AA10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AA10" s="5" t="s">
+      <c r="AB10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AB10" s="5" t="s">
+      <c r="AC10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AC10" s="5" t="s">
+      <c r="AD10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AD10" s="5" t="s">
+      <c r="AE10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AE10" s="5" t="s">
+      <c r="AF10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AF10" s="5" t="s">
+      <c r="AG10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AG10" s="5" t="s">
+      <c r="AH10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AH10" s="5" t="s">
+      <c r="AI10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AI10" s="5" t="s">
+      <c r="AJ10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AJ10" s="5" t="s">
+      <c r="AK10" s="5" t="s">
         <v>42</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
     <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
     <mergeCell ref="U8:U9"/>
     <mergeCell ref="V8:V9"/>
     <mergeCell ref="W8:W9"/>
     <mergeCell ref="X8:X9"/>
     <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
     <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoKetQuaHocTapIELTS.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoKetQuaHocTapIELTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60682F78-EF53-4FD2-AC44-AEAC34BDCCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF25CC47-CE6D-48B8-B278-E1769B7B22B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0D544DFD-F0B4-4797-9334-D0119CA48DC0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
   <si>
     <t>BÁO CÁO KẾT QUẢ HỌC TẬP (IELTS)</t>
   </si>
@@ -162,15 +162,6 @@
     <t>[Percentage]</t>
   </si>
   <si>
-    <t>10 hs</t>
-  </si>
-  <si>
-    <t>5 hs</t>
-  </si>
-  <si>
-    <t>2 hs</t>
-  </si>
-  <si>
     <t>0 hs</t>
   </si>
   <si>
@@ -229,6 +220,9 @@
   </si>
   <si>
     <t>UserName</t>
+  </si>
+  <si>
+    <t>Số Điện Thoại</t>
   </si>
 </sst>
 </file>
@@ -864,25 +858,25 @@
         <v>2</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="L2" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="M2" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N2" s="8"/>
       <c r="O2" s="2"/>
@@ -918,7 +912,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="8">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
@@ -961,13 +955,13 @@
       <c r="D4" s="15"/>
       <c r="E4" s="16"/>
       <c r="F4" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="8"/>
@@ -1008,13 +1002,13 @@
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
       <c r="F5" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="8"/>
@@ -1055,13 +1049,13 @@
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="8"/>
@@ -1145,28 +1139,28 @@
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="J8" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>64</v>
-      </c>
       <c r="M8" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N8" s="21"/>
       <c r="O8" s="23"/>
@@ -1203,25 +1197,25 @@
         <v>45</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N9" s="22"/>
       <c r="O9" s="24"/>
@@ -1253,13 +1247,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>10</v>
